--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/34.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/34.xlsx
@@ -426,13 +426,13 @@
         <v>-24.98350908747489</v>
       </c>
       <c r="E2">
-        <v>-12.78062822754951</v>
+        <v>-15.63666885707709</v>
       </c>
       <c r="F2">
-        <v>-1.719159063586684</v>
+        <v>-1.886067639944159</v>
       </c>
       <c r="G2">
-        <v>-7.684575188791723</v>
+        <v>-8.252995857884587</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-25.50548457570983</v>
       </c>
       <c r="E3">
-        <v>-13.73422522713672</v>
+        <v>-16.2473154631154</v>
       </c>
       <c r="F3">
-        <v>-1.827801933566048</v>
+        <v>-2.024190449054352</v>
       </c>
       <c r="G3">
-        <v>-7.88327413205878</v>
+        <v>-8.436893352045562</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-26.01540161660481</v>
       </c>
       <c r="E4">
-        <v>-14.26632092303798</v>
+        <v>-17.04407782239496</v>
       </c>
       <c r="F4">
-        <v>-1.580559114852479</v>
+        <v>-1.890217760632185</v>
       </c>
       <c r="G4">
-        <v>-7.432189128514306</v>
+        <v>-8.003489972226335</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-26.37788286251192</v>
       </c>
       <c r="E5">
-        <v>-14.40073508853365</v>
+        <v>-17.97778576414049</v>
       </c>
       <c r="F5">
-        <v>-1.729734830218225</v>
+        <v>-2.12488099196684</v>
       </c>
       <c r="G5">
-        <v>-7.238826784656554</v>
+        <v>-8.037591901826367</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-26.58502085617533</v>
       </c>
       <c r="E6">
-        <v>-14.72526364981934</v>
+        <v>-18.58039432881518</v>
       </c>
       <c r="F6">
-        <v>-1.680292065047331</v>
+        <v>-2.187767331717767</v>
       </c>
       <c r="G6">
-        <v>-7.154788586142155</v>
+        <v>-8.300257206003222</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-26.58162183217288</v>
       </c>
       <c r="E7">
-        <v>-16.65569777760112</v>
+        <v>-19.03637996206954</v>
       </c>
       <c r="F7">
-        <v>-1.79340149206259</v>
+        <v>-1.822405119936809</v>
       </c>
       <c r="G7">
-        <v>-7.093202507475094</v>
+        <v>-7.993498745788814</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-26.3613880626331</v>
       </c>
       <c r="E8">
-        <v>-15.90455526547483</v>
+        <v>-19.39282067968728</v>
       </c>
       <c r="F8">
-        <v>-1.70330079802749</v>
+        <v>-1.779576040109866</v>
       </c>
       <c r="G8">
-        <v>-7.132108038652609</v>
+        <v>-7.612908498957581</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-25.89915963798922</v>
       </c>
       <c r="E9">
-        <v>-17.66456480245195</v>
+        <v>-20.23960456285557</v>
       </c>
       <c r="F9">
-        <v>-1.384418281217612</v>
+        <v>-1.503370183524816</v>
       </c>
       <c r="G9">
-        <v>-6.629163339235451</v>
+        <v>-7.503359236517558</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-25.21568900339086</v>
       </c>
       <c r="E10">
-        <v>-17.79208210203394</v>
+        <v>-20.72256631577361</v>
       </c>
       <c r="F10">
-        <v>-1.713111981546248</v>
+        <v>-1.583508102806445</v>
       </c>
       <c r="G10">
-        <v>-6.515187877409423</v>
+        <v>-7.939834802597228</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-24.32803290052985</v>
       </c>
       <c r="E11">
-        <v>-18.62748140154694</v>
+        <v>-21.95662982455188</v>
       </c>
       <c r="F11">
-        <v>-1.295214709079745</v>
+        <v>-1.9370925868544</v>
       </c>
       <c r="G11">
-        <v>-6.177849908048767</v>
+        <v>-7.459315738663094</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-23.29500564813829</v>
       </c>
       <c r="E12">
-        <v>-19.79304268401118</v>
+        <v>-22.58150489592229</v>
       </c>
       <c r="F12">
-        <v>-1.291420786374923</v>
+        <v>-1.840934870370031</v>
       </c>
       <c r="G12">
-        <v>-6.199567086786386</v>
+        <v>-7.05274433043966</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-22.17154430586186</v>
       </c>
       <c r="E13">
-        <v>-19.46304372612422</v>
+        <v>-21.3664338071322</v>
       </c>
       <c r="F13">
-        <v>-1.148495931430702</v>
+        <v>-1.377347337067316</v>
       </c>
       <c r="G13">
-        <v>-5.913860385656204</v>
+        <v>-6.428994513748958</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-21.03517784461982</v>
       </c>
       <c r="E14">
-        <v>-20.33943024388065</v>
+        <v>-23.39111906443562</v>
       </c>
       <c r="F14">
-        <v>-0.8178075223961253</v>
+        <v>-1.48025293441489</v>
       </c>
       <c r="G14">
-        <v>-5.669091890664649</v>
+        <v>-7.027822543620027</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.95265107494104</v>
       </c>
       <c r="E15">
-        <v>-21.53072231565647</v>
+        <v>-23.63978662914482</v>
       </c>
       <c r="F15">
-        <v>-0.6857790122683288</v>
+        <v>-1.189100844781128</v>
       </c>
       <c r="G15">
-        <v>-5.25696207648078</v>
+        <v>-5.962267182531428</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.98664459099773</v>
       </c>
       <c r="E16">
-        <v>-22.62356083403153</v>
+        <v>-24.81614832211735</v>
       </c>
       <c r="F16">
-        <v>-0.3542862584856339</v>
+        <v>-0.8318500066083825</v>
       </c>
       <c r="G16">
-        <v>-5.775357091929716</v>
+        <v>-5.440151113896351</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.18638328345927</v>
       </c>
       <c r="E17">
-        <v>-24.0003844859016</v>
+        <v>-24.90418638530046</v>
       </c>
       <c r="F17">
-        <v>0.1915631281194891</v>
+        <v>-0.6665642019929915</v>
       </c>
       <c r="G17">
-        <v>-5.408081859257431</v>
+        <v>-5.993810060429603</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.58081499569788</v>
       </c>
       <c r="E18">
-        <v>-24.54293642828658</v>
+        <v>-26.35216142077905</v>
       </c>
       <c r="F18">
-        <v>0.359943713351739</v>
+        <v>-0.2753809498993698</v>
       </c>
       <c r="G18">
-        <v>-4.663262081650042</v>
+        <v>-5.706024336700759</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.18856091852968</v>
       </c>
       <c r="E19">
-        <v>-25.66976567256321</v>
+        <v>-27.24510856798153</v>
       </c>
       <c r="F19">
-        <v>0.80724968535243</v>
+        <v>-0.2459266901580278</v>
       </c>
       <c r="G19">
-        <v>-4.971371244444472</v>
+        <v>-5.524861353155222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-16.99964491480576</v>
       </c>
       <c r="E20">
-        <v>-25.28153506741162</v>
+        <v>-26.59264603295639</v>
       </c>
       <c r="F20">
-        <v>1.227995713317161</v>
+        <v>0.3395219717705228</v>
       </c>
       <c r="G20">
-        <v>-4.431752321543269</v>
+        <v>-5.122080519574253</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.00066692395447</v>
       </c>
       <c r="E21">
-        <v>-26.80193398769488</v>
+        <v>-28.24147700457119</v>
       </c>
       <c r="F21">
-        <v>1.251995173711068</v>
+        <v>0.4462819626433231</v>
       </c>
       <c r="G21">
-        <v>-4.895639204688105</v>
+        <v>-5.586000508174482</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.14729952532636</v>
       </c>
       <c r="E22">
-        <v>-27.21821396084998</v>
+        <v>-28.61624898497198</v>
       </c>
       <c r="F22">
-        <v>1.505510390398634</v>
+        <v>0.9128847532922286</v>
       </c>
       <c r="G22">
-        <v>-4.596802879949173</v>
+        <v>-5.716008942047201</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.40067563309807</v>
       </c>
       <c r="E23">
-        <v>-27.21563273066561</v>
+        <v>-29.36243281805987</v>
       </c>
       <c r="F23">
-        <v>1.740168651528873</v>
+        <v>1.166795929598333</v>
       </c>
       <c r="G23">
-        <v>-4.684558821104174</v>
+        <v>-5.716767056975694</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.69816115376583</v>
       </c>
       <c r="E24">
-        <v>-28.60780338094767</v>
+        <v>-30.01197222311306</v>
       </c>
       <c r="F24">
-        <v>1.782547927856095</v>
+        <v>1.093984091627062</v>
       </c>
       <c r="G24">
-        <v>-5.51097361461798</v>
+        <v>-5.802708819175174</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.99486645052399</v>
       </c>
       <c r="E25">
-        <v>-28.37600891039106</v>
+        <v>-29.45656394302031</v>
       </c>
       <c r="F25">
-        <v>1.85355889509368</v>
+        <v>1.239664096552994</v>
       </c>
       <c r="G25">
-        <v>-5.211561254955215</v>
+        <v>-5.313171829192065</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.23337354120806</v>
       </c>
       <c r="E26">
-        <v>-28.31570775050492</v>
+        <v>-29.62426465670936</v>
       </c>
       <c r="F26">
-        <v>1.972520737809717</v>
+        <v>1.367360245164149</v>
       </c>
       <c r="G26">
-        <v>-5.250052967940321</v>
+        <v>-5.602079827858723</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.38205607774492</v>
       </c>
       <c r="E27">
-        <v>-29.0769985728824</v>
+        <v>-29.05278482236339</v>
       </c>
       <c r="F27">
-        <v>2.268286005509669</v>
+        <v>1.38361115687227</v>
       </c>
       <c r="G27">
-        <v>-5.416662793295222</v>
+        <v>-5.978280291304882</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.40582219120104</v>
       </c>
       <c r="E28">
-        <v>-28.1723498488441</v>
+        <v>-29.16450227613261</v>
       </c>
       <c r="F28">
-        <v>2.124383677030145</v>
+        <v>1.249132335966993</v>
       </c>
       <c r="G28">
-        <v>-5.097565929855951</v>
+        <v>-5.521597155253501</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.29866237982131</v>
       </c>
       <c r="E29">
-        <v>-28.22674135015023</v>
+        <v>-30.08026840385974</v>
       </c>
       <c r="F29">
-        <v>1.678688879627899</v>
+        <v>1.567278434155782</v>
       </c>
       <c r="G29">
-        <v>-5.185811831750764</v>
+        <v>-5.823535461162729</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-18.05703506478099</v>
       </c>
       <c r="E30">
-        <v>-28.64433458076755</v>
+        <v>-28.33630325029181</v>
       </c>
       <c r="F30">
-        <v>1.990971793339673</v>
+        <v>1.223726307723132</v>
       </c>
       <c r="G30">
-        <v>-5.323487489092434</v>
+        <v>-6.206042513861201</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-17.70293432914928</v>
       </c>
       <c r="E31">
-        <v>-27.95676278676094</v>
+        <v>-29.8817536887855</v>
       </c>
       <c r="F31">
-        <v>1.757088884098455</v>
+        <v>1.291582851890856</v>
       </c>
       <c r="G31">
-        <v>-5.259706518732836</v>
+        <v>-6.21244841947969</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-17.25809409281065</v>
       </c>
       <c r="E32">
-        <v>-27.46939482863343</v>
+        <v>-28.92441164119395</v>
       </c>
       <c r="F32">
-        <v>1.786199371367635</v>
+        <v>1.092917154412256</v>
       </c>
       <c r="G32">
-        <v>-5.281933521483502</v>
+        <v>-6.018407413786388</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.75705181954471</v>
       </c>
       <c r="E33">
-        <v>-27.85833187573022</v>
+        <v>-28.59317188142889</v>
       </c>
       <c r="F33">
-        <v>1.825558420144251</v>
+        <v>1.098094450679753</v>
       </c>
       <c r="G33">
-        <v>-4.922984310842485</v>
+        <v>-6.415470935221036</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.22676237269249</v>
       </c>
       <c r="E34">
-        <v>-26.8118060610316</v>
+        <v>-27.96681599905796</v>
       </c>
       <c r="F34">
-        <v>1.697608791107839</v>
+        <v>0.8567794291006181</v>
       </c>
       <c r="G34">
-        <v>-4.355454178499686</v>
+        <v>-5.673955082061839</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.69461370519699</v>
       </c>
       <c r="E35">
-        <v>-26.3047799972368</v>
+        <v>-27.52052582865404</v>
       </c>
       <c r="F35">
-        <v>1.587876617993795</v>
+        <v>0.8016913400796454</v>
       </c>
       <c r="G35">
-        <v>-4.702886001209579</v>
+        <v>-6.558522918518483</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.1807379347166</v>
       </c>
       <c r="E36">
-        <v>-26.07563015550066</v>
+        <v>-28.19851537166042</v>
       </c>
       <c r="F36">
-        <v>1.421053363478808</v>
+        <v>0.8700747259155501</v>
       </c>
       <c r="G36">
-        <v>-4.702177544464175</v>
+        <v>-5.992840070586597</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.69978365715486</v>
       </c>
       <c r="E37">
-        <v>-25.66428169053992</v>
+        <v>-27.88266789504743</v>
       </c>
       <c r="F37">
-        <v>1.43733740988304</v>
+        <v>0.8382438800955764</v>
       </c>
       <c r="G37">
-        <v>-4.004420482243066</v>
+        <v>-5.232033668570068</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.26512857089219</v>
       </c>
       <c r="E38">
-        <v>-25.34937160804652</v>
+        <v>-26.82148340998599</v>
       </c>
       <c r="F38">
-        <v>1.407521153586675</v>
+        <v>1.048064373020274</v>
       </c>
       <c r="G38">
-        <v>-3.32685774781151</v>
+        <v>-4.909209130853577</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.88211503338215</v>
       </c>
       <c r="E39">
-        <v>-25.31043126005456</v>
+        <v>-26.77216832804246</v>
       </c>
       <c r="F39">
-        <v>1.304072975590267</v>
+        <v>0.7765338220566244</v>
       </c>
       <c r="G39">
-        <v>-3.321968072050006</v>
+        <v>-5.152249521073633</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.56101840740268</v>
       </c>
       <c r="E40">
-        <v>-24.64444670164252</v>
+        <v>-25.77469494379494</v>
       </c>
       <c r="F40">
-        <v>1.234862879086368</v>
+        <v>0.7497328231064492</v>
       </c>
       <c r="G40">
-        <v>-3.886094963578435</v>
+        <v>-5.078298554817392</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.30079487189595</v>
       </c>
       <c r="E41">
-        <v>-24.57898760986164</v>
+        <v>-25.7482260132201</v>
       </c>
       <c r="F41">
-        <v>1.455264937214427</v>
+        <v>0.650603752748238</v>
       </c>
       <c r="G41">
-        <v>-2.998415214314877</v>
+        <v>-4.13499170885746</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.11131202769024</v>
       </c>
       <c r="E42">
-        <v>-23.86163657078059</v>
+        <v>-25.95826569464387</v>
       </c>
       <c r="F42">
-        <v>1.220924769166864</v>
+        <v>0.2433766807971954</v>
       </c>
       <c r="G42">
-        <v>-3.044445039492903</v>
+        <v>-4.75330229922714</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.98797863823194</v>
       </c>
       <c r="E43">
-        <v>-23.5597186802152</v>
+        <v>-25.13776054614209</v>
       </c>
       <c r="F43">
-        <v>0.9106514747742811</v>
+        <v>0.3650787628816932</v>
       </c>
       <c r="G43">
-        <v>-2.936560981459134</v>
+        <v>-5.067526039632604</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.93599562518553</v>
       </c>
       <c r="E44">
-        <v>-23.85447705337446</v>
+        <v>-24.64084203633241</v>
       </c>
       <c r="F44">
-        <v>0.9195050655754022</v>
+        <v>0.3041390865273447</v>
       </c>
       <c r="G44">
-        <v>-3.357957012607424</v>
+        <v>-3.827501618078874</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.94207731588546</v>
       </c>
       <c r="E45">
-        <v>-23.09752450909633</v>
+        <v>-24.2093780898296</v>
       </c>
       <c r="F45">
-        <v>1.058481921477881</v>
+        <v>0.2005799072989617</v>
       </c>
       <c r="G45">
-        <v>-3.074908679545276</v>
+        <v>-5.053383389088838</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.0013921947251</v>
       </c>
       <c r="E46">
-        <v>-22.3115852026951</v>
+        <v>-24.09409672701633</v>
       </c>
       <c r="F46">
-        <v>1.086840251145319</v>
+        <v>0.2821078270824891</v>
       </c>
       <c r="G46">
-        <v>-2.68515484266134</v>
+        <v>-4.363366382338544</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.09260538555083</v>
       </c>
       <c r="E47">
-        <v>-21.96109037144943</v>
+        <v>-22.82942073394621</v>
       </c>
       <c r="F47">
-        <v>0.8038550357357577</v>
+        <v>0.3779598759952255</v>
       </c>
       <c r="G47">
-        <v>-2.405393881319689</v>
+        <v>-4.637903302819224</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.20509906648487</v>
       </c>
       <c r="E48">
-        <v>-21.41761009189288</v>
+        <v>-22.28106781635741</v>
       </c>
       <c r="F48">
-        <v>0.9728767773377744</v>
+        <v>0.2744073237060649</v>
       </c>
       <c r="G48">
-        <v>-2.300674704821463</v>
+        <v>-4.79377371844473</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.31782154527643</v>
       </c>
       <c r="E49">
-        <v>-20.46617317440733</v>
+        <v>-22.24537438422895</v>
       </c>
       <c r="F49">
-        <v>0.7636460820038697</v>
+        <v>-0.05853010282711242</v>
       </c>
       <c r="G49">
-        <v>-3.185696086016987</v>
+        <v>-4.240396168282316</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.42122868823549</v>
       </c>
       <c r="E50">
-        <v>-20.71499470723279</v>
+        <v>-22.17577173873106</v>
       </c>
       <c r="F50">
-        <v>0.56879750151737</v>
+        <v>0.2626146853598111</v>
       </c>
       <c r="G50">
-        <v>-2.862600083566276</v>
+        <v>-4.141116218105112</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.50222886016427</v>
       </c>
       <c r="E51">
-        <v>-20.67990356214735</v>
+        <v>-21.72707694862906</v>
       </c>
       <c r="F51">
-        <v>1.019898224590285</v>
+        <v>0.3049409461732547</v>
       </c>
       <c r="G51">
-        <v>-3.027342761237028</v>
+        <v>-4.205165342653392</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.5578660940059</v>
       </c>
       <c r="E52">
-        <v>-19.6766880728581</v>
+        <v>-21.96031147392011</v>
       </c>
       <c r="F52">
-        <v>0.8174303207328359</v>
+        <v>0.0908908092898624</v>
       </c>
       <c r="G52">
-        <v>-2.964213968348666</v>
+        <v>-5.331419556204528</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.58664909795688</v>
       </c>
       <c r="E53">
-        <v>-18.91814603420327</v>
+        <v>-20.81459396455749</v>
       </c>
       <c r="F53">
-        <v>0.7202561974452316</v>
+        <v>0.5789184944447744</v>
       </c>
       <c r="G53">
-        <v>-2.874554463508584</v>
+        <v>-4.787351260098544</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.59132925956044</v>
       </c>
       <c r="E54">
-        <v>-18.70566097681536</v>
+        <v>-20.88759749403514</v>
       </c>
       <c r="F54">
-        <v>0.9063572181581685</v>
+        <v>0.3319465518719213</v>
       </c>
       <c r="G54">
-        <v>-3.205281273427315</v>
+        <v>-4.710215549033525</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.5809080225818</v>
       </c>
       <c r="E55">
-        <v>-18.93265979339786</v>
+        <v>-19.36984773104637</v>
       </c>
       <c r="F55">
-        <v>1.106624978193783</v>
+        <v>0.406821024676163</v>
       </c>
       <c r="G55">
-        <v>-3.253760902304402</v>
+        <v>-5.012633884045949</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-13.56148748645825</v>
       </c>
       <c r="E56">
-        <v>-18.09228822942443</v>
+        <v>-21.11240000072391</v>
       </c>
       <c r="F56">
-        <v>1.077095337018786</v>
+        <v>0.464945080228396</v>
       </c>
       <c r="G56">
-        <v>-3.769580313323785</v>
+        <v>-4.46581452459683</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.54799771448159</v>
       </c>
       <c r="E57">
-        <v>-18.61363785650549</v>
+        <v>-19.18362782290295</v>
       </c>
       <c r="F57">
-        <v>0.9966625189417594</v>
+        <v>-0.1664216435721368</v>
       </c>
       <c r="G57">
-        <v>-3.488650729406772</v>
+        <v>-4.633884300534549</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.54670238346416</v>
       </c>
       <c r="E58">
-        <v>-18.10071119107869</v>
+        <v>-19.75193319696955</v>
       </c>
       <c r="F58">
-        <v>1.080445254795707</v>
+        <v>0.1365645027780187</v>
       </c>
       <c r="G58">
-        <v>-3.850423835392788</v>
+        <v>-5.357079594679419</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.57276220353001</v>
       </c>
       <c r="E59">
-        <v>-17.48633312245806</v>
+        <v>-19.71311058930179</v>
       </c>
       <c r="F59">
-        <v>1.140294799647971</v>
+        <v>0.6207659588993998</v>
       </c>
       <c r="G59">
-        <v>-4.048785103014839</v>
+        <v>-5.363634474847176</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.62746526262366</v>
       </c>
       <c r="E60">
-        <v>-16.90091011664246</v>
+        <v>-18.5546590110296</v>
       </c>
       <c r="F60">
-        <v>1.157422124068254</v>
+        <v>0.3879756662624743</v>
       </c>
       <c r="G60">
-        <v>-4.457978463305375</v>
+        <v>-5.277004119175528</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.72076165815042</v>
       </c>
       <c r="E61">
-        <v>-16.74716389560805</v>
+        <v>-19.32933600257375</v>
       </c>
       <c r="F61">
-        <v>1.014636434847703</v>
+        <v>0.4517425605625774</v>
       </c>
       <c r="G61">
-        <v>-4.39082073649572</v>
+        <v>-5.731088476978582</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.84580869924112</v>
       </c>
       <c r="E62">
-        <v>-16.45840122203494</v>
+        <v>-19.18577884805659</v>
       </c>
       <c r="F62">
-        <v>0.9737581602543531</v>
+        <v>0.6384019009050013</v>
       </c>
       <c r="G62">
-        <v>-4.825866146902425</v>
+        <v>-5.532134621705</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.00465087831873</v>
       </c>
       <c r="E63">
-        <v>-16.28059069012376</v>
+        <v>-17.95644759461634</v>
       </c>
       <c r="F63">
-        <v>1.073824942512533</v>
+        <v>0.2666943948185987</v>
       </c>
       <c r="G63">
-        <v>-4.895612720323791</v>
+        <v>-5.773602502793902</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.18232195236401</v>
       </c>
       <c r="E64">
-        <v>-16.11433682388016</v>
+        <v>-18.23678277806118</v>
       </c>
       <c r="F64">
-        <v>0.9292632335803804</v>
+        <v>0.2302752219545184</v>
       </c>
       <c r="G64">
-        <v>-5.078050263901947</v>
+        <v>-6.140990294014522</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.373814157286</v>
       </c>
       <c r="E65">
-        <v>-15.09813367113691</v>
+        <v>-18.00732500009252</v>
       </c>
       <c r="F65">
-        <v>0.9896396201008252</v>
+        <v>0.440113938962078</v>
       </c>
       <c r="G65">
-        <v>-5.591194754125599</v>
+        <v>-6.659362135644683</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.56100818629379</v>
       </c>
       <c r="E66">
-        <v>-15.4808757657912</v>
+        <v>-17.90113228461265</v>
       </c>
       <c r="F66">
-        <v>1.086265364167776</v>
+        <v>0.166302892538521</v>
       </c>
       <c r="G66">
-        <v>-4.921382006801477</v>
+        <v>-6.486869470866497</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.73893906526959</v>
       </c>
       <c r="E67">
-        <v>-15.00043184442142</v>
+        <v>-18.18836433397116</v>
       </c>
       <c r="F67">
-        <v>0.8730319975435444</v>
+        <v>0.4275724564836935</v>
       </c>
       <c r="G67">
-        <v>-5.719845864327216</v>
+        <v>-6.621618605951452</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.89382547834866</v>
       </c>
       <c r="E68">
-        <v>-15.61861835968251</v>
+        <v>-17.63203677365485</v>
       </c>
       <c r="F68">
-        <v>0.6052945409173134</v>
+        <v>0.2438488502167911</v>
       </c>
       <c r="G68">
-        <v>-5.043964887029611</v>
+        <v>-6.429408331941367</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.02236000006428</v>
       </c>
       <c r="E69">
-        <v>-15.30976737541138</v>
+        <v>-17.13083885590792</v>
       </c>
       <c r="F69">
-        <v>0.8673460836907286</v>
+        <v>0.3277972595512986</v>
       </c>
       <c r="G69">
-        <v>-5.786821511132212</v>
+        <v>-6.537315563793912</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.11422417786923</v>
       </c>
       <c r="E70">
-        <v>-15.92207593141051</v>
+        <v>-17.9274925318113</v>
       </c>
       <c r="F70">
-        <v>0.8409476712983139</v>
+        <v>0.02667742495965033</v>
       </c>
       <c r="G70">
-        <v>-6.240187480553244</v>
+        <v>-6.672306368703233</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.16834406062793</v>
       </c>
       <c r="E71">
-        <v>-15.42146218681057</v>
+        <v>-17.69162243464778</v>
       </c>
       <c r="F71">
-        <v>0.339880654855935</v>
+        <v>0.0175040843410486</v>
       </c>
       <c r="G71">
-        <v>-5.718928843212838</v>
+        <v>-6.306325559336804</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.18292402743381</v>
       </c>
       <c r="E72">
-        <v>-15.65672999693106</v>
+        <v>-17.91218176119136</v>
       </c>
       <c r="F72">
-        <v>0.6339055226426055</v>
+        <v>-0.08170616602263699</v>
       </c>
       <c r="G72">
-        <v>-5.489613974798602</v>
+        <v>-6.086078275154631</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.1625851447485</v>
       </c>
       <c r="E73">
-        <v>-15.47835793424294</v>
+        <v>-17.96730687528673</v>
       </c>
       <c r="F73">
-        <v>0.4173379772221056</v>
+        <v>-0.410669914124585</v>
       </c>
       <c r="G73">
-        <v>-5.200888056136605</v>
+        <v>-5.957235153311736</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.11345569776761</v>
       </c>
       <c r="E74">
-        <v>-15.4974046959192</v>
+        <v>-17.99017566902547</v>
       </c>
       <c r="F74">
-        <v>0.3766991008081646</v>
+        <v>-0.3307084370997516</v>
       </c>
       <c r="G74">
-        <v>-5.17428782272856</v>
+        <v>-6.206052445497819</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.04225508179704</v>
       </c>
       <c r="E75">
-        <v>-15.80342085546153</v>
+        <v>-17.68760114972897</v>
       </c>
       <c r="F75">
-        <v>0.1268137900796658</v>
+        <v>-0.2973285442365427</v>
       </c>
       <c r="G75">
-        <v>-5.509768576041685</v>
+        <v>-7.064155780913528</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.95903478894136</v>
       </c>
       <c r="E76">
-        <v>-16.43267043272336</v>
+        <v>-18.38924291247741</v>
       </c>
       <c r="F76">
-        <v>0.06568690269228464</v>
+        <v>-0.1890741785690921</v>
       </c>
       <c r="G76">
-        <v>-5.516095028567232</v>
+        <v>-6.193396229901185</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.86815581117424</v>
       </c>
       <c r="E77">
-        <v>-16.45267723088925</v>
+        <v>-18.79596327700232</v>
       </c>
       <c r="F77">
-        <v>0.3038972032457273</v>
+        <v>-0.3771881320708318</v>
       </c>
       <c r="G77">
-        <v>-5.118246907839778</v>
+        <v>-6.157324525705286</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-14.7788518519575</v>
       </c>
       <c r="E78">
-        <v>-15.81902597689196</v>
+        <v>-18.63548321511849</v>
       </c>
       <c r="F78">
-        <v>0.2743087479851317</v>
+        <v>-0.871891630124905</v>
       </c>
       <c r="G78">
-        <v>-4.900687786635493</v>
+        <v>-6.091851866575119</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-14.69024058539485</v>
       </c>
       <c r="E79">
-        <v>-16.76105725386358</v>
+        <v>-18.71858524163325</v>
       </c>
       <c r="F79">
-        <v>-0.1705576820143148</v>
+        <v>-0.7249856414428295</v>
       </c>
       <c r="G79">
-        <v>-4.941543229135639</v>
+        <v>-5.988734994117901</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-14.60782927238675</v>
       </c>
       <c r="E80">
-        <v>-17.64144694264279</v>
+        <v>-18.71879355143761</v>
       </c>
       <c r="F80">
-        <v>-0.07652886975514007</v>
+        <v>-0.9755468999720127</v>
       </c>
       <c r="G80">
-        <v>-4.186745467272886</v>
+        <v>-5.873756436993473</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-14.52438449934465</v>
       </c>
       <c r="E81">
-        <v>-17.92304557033577</v>
+        <v>-19.67458686091853</v>
       </c>
       <c r="F81">
-        <v>-0.2566921529248102</v>
+        <v>-0.9849339593805367</v>
       </c>
       <c r="G81">
-        <v>-4.546062148468764</v>
+        <v>-5.378118111581488</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-14.44179018723079</v>
       </c>
       <c r="E82">
-        <v>-19.26455618189402</v>
+        <v>-20.56518373011103</v>
       </c>
       <c r="F82">
-        <v>-0.189202575516526</v>
+        <v>-0.8834688929464308</v>
       </c>
       <c r="G82">
-        <v>-4.679099731509916</v>
+        <v>-5.436605519623791</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.34915306019557</v>
       </c>
       <c r="E83">
-        <v>-19.51114970550771</v>
+        <v>-20.22639500417519</v>
       </c>
       <c r="F83">
-        <v>-0.6667389875149823</v>
+        <v>-0.8721716183070513</v>
       </c>
       <c r="G83">
-        <v>-4.092106901941741</v>
+        <v>-5.228305994292849</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.2475677026333</v>
       </c>
       <c r="E84">
-        <v>-19.92659643944539</v>
+        <v>-22.90975133436828</v>
       </c>
       <c r="F84">
-        <v>-0.6286067508619125</v>
+        <v>-1.160422765296209</v>
       </c>
       <c r="G84">
-        <v>-4.204407227724898</v>
+        <v>-4.540917560700736</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.12583050235444</v>
       </c>
       <c r="E85">
-        <v>-20.63546564671008</v>
+        <v>-22.29044175755329</v>
       </c>
       <c r="F85">
-        <v>-0.7977361802262932</v>
+        <v>-1.580963358145045</v>
       </c>
       <c r="G85">
-        <v>-3.586440934091303</v>
+        <v>-4.982180175630193</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.98644316775864</v>
       </c>
       <c r="E86">
-        <v>-21.63383114033712</v>
+        <v>-23.6757291273437</v>
       </c>
       <c r="F86">
-        <v>-0.9654201084727888</v>
+        <v>-1.715662524779467</v>
       </c>
       <c r="G86">
-        <v>-3.404864132353357</v>
+        <v>-4.800480883707293</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.82070775749436</v>
       </c>
       <c r="E87">
-        <v>-22.63449257028604</v>
+        <v>-25.64193367131206</v>
       </c>
       <c r="F87">
-        <v>-1.249136772299022</v>
+        <v>-1.775260245941281</v>
       </c>
       <c r="G87">
-        <v>-3.389423747958196</v>
+        <v>-6.030093639540016</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.63436127863392</v>
       </c>
       <c r="E88">
-        <v>-23.51572002675667</v>
+        <v>-25.54162797204217</v>
       </c>
       <c r="F88">
-        <v>-1.568199873202711</v>
+        <v>-1.94843127986392</v>
       </c>
       <c r="G88">
-        <v>-3.43601305533236</v>
+        <v>-4.867234723961158</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.42330095899474</v>
       </c>
       <c r="E89">
-        <v>-24.87996357783344</v>
+        <v>-27.35941178040914</v>
       </c>
       <c r="F89">
-        <v>-1.62399704472048</v>
+        <v>-1.871156198326365</v>
       </c>
       <c r="G89">
-        <v>-3.15161070914465</v>
+        <v>-4.614878458593593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.19700025091026</v>
       </c>
       <c r="E90">
-        <v>-26.35338863723513</v>
+        <v>-27.83985117330491</v>
       </c>
       <c r="F90">
-        <v>-1.800625684182404</v>
+        <v>-2.113479343034708</v>
       </c>
       <c r="G90">
-        <v>-3.126960387059237</v>
+        <v>-4.508788716242109</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.95711340904382</v>
       </c>
       <c r="E91">
-        <v>-28.20029506194543</v>
+        <v>-29.95482967384728</v>
       </c>
       <c r="F91">
-        <v>-1.834480231567417</v>
+        <v>-2.639920909759641</v>
       </c>
       <c r="G91">
-        <v>-3.305127326891734</v>
+        <v>-3.947962438616335</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.71643489384575</v>
       </c>
       <c r="E92">
-        <v>-29.8772071008818</v>
+        <v>-31.58426066281321</v>
       </c>
       <c r="F92">
-        <v>-2.165041900389366</v>
+        <v>-2.774715338645385</v>
       </c>
       <c r="G92">
-        <v>-2.813104117208632</v>
+        <v>-4.952418371232144</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.48262076915593</v>
       </c>
       <c r="E93">
-        <v>-31.71782573943245</v>
+        <v>-32.88688979654162</v>
       </c>
       <c r="F93">
-        <v>-2.314865399064101</v>
+        <v>-2.800559573245327</v>
       </c>
       <c r="G93">
-        <v>-2.613951629202695</v>
+        <v>-4.959128847040247</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.26971617944012</v>
       </c>
       <c r="E94">
-        <v>-33.86322652835834</v>
+        <v>-34.70691067106838</v>
       </c>
       <c r="F94">
-        <v>-2.506567840154768</v>
+        <v>-2.865017325959365</v>
       </c>
       <c r="G94">
-        <v>-3.438247673571368</v>
+        <v>-4.834394112211587</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.088721081386</v>
       </c>
       <c r="E95">
-        <v>-35.67422894689883</v>
+        <v>-36.39448047358179</v>
       </c>
       <c r="F95">
-        <v>-2.634361736119454</v>
+        <v>-3.226675907082406</v>
       </c>
       <c r="G95">
-        <v>-3.673326201769476</v>
+        <v>-4.391059095774548</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.95485557220719</v>
       </c>
       <c r="E96">
-        <v>-37.51724088396254</v>
+        <v>-38.71332181700146</v>
       </c>
       <c r="F96">
-        <v>-3.049971057819424</v>
+        <v>-3.715636333932871</v>
       </c>
       <c r="G96">
-        <v>-3.302962230109051</v>
+        <v>-5.725404270287653</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.87532416051174</v>
       </c>
       <c r="E97">
-        <v>-39.07498839362405</v>
+        <v>-40.48665638874615</v>
       </c>
       <c r="F97">
-        <v>-3.240307521062875</v>
+        <v>-3.876975796241325</v>
       </c>
       <c r="G97">
-        <v>-3.835758118653816</v>
+        <v>-5.040187554569302</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.86726094090107</v>
       </c>
       <c r="E98">
-        <v>-41.72236146935219</v>
+        <v>-42.39579310326986</v>
       </c>
       <c r="F98">
-        <v>-3.200260927341936</v>
+        <v>-4.101360644842043</v>
       </c>
       <c r="G98">
-        <v>-4.572069794225278</v>
+        <v>-5.196134112742211</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.92423518948475</v>
       </c>
       <c r="E99">
-        <v>-44.08267457773411</v>
+        <v>-45.29417270053215</v>
       </c>
       <c r="F99">
-        <v>-3.497983627214703</v>
+        <v>-4.298973487351685</v>
       </c>
       <c r="G99">
-        <v>-4.692096933297094</v>
+        <v>-6.452158400887239</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.06875788163859</v>
       </c>
       <c r="E100">
-        <v>-47.15170971797546</v>
+        <v>-47.76285445615462</v>
       </c>
       <c r="F100">
-        <v>-3.630590337789654</v>
+        <v>-4.456702096151337</v>
       </c>
       <c r="G100">
-        <v>-4.569573642888668</v>
+        <v>-6.471783314844038</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.26137052156268</v>
       </c>
       <c r="E101">
-        <v>-48.46506114603552</v>
+        <v>-49.27389075642702</v>
       </c>
       <c r="F101">
-        <v>-3.807431867674098</v>
+        <v>-4.554679735819656</v>
       </c>
       <c r="G101">
-        <v>-5.218232004216846</v>
+        <v>-6.532604657491529</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.55616033807458</v>
       </c>
       <c r="E102">
-        <v>-51.41136218736548</v>
+        <v>-52.20562256475581</v>
       </c>
       <c r="F102">
-        <v>-4.001930048749213</v>
+        <v>-4.443153318911148</v>
       </c>
       <c r="G102">
-        <v>-5.597964819753408</v>
+        <v>-7.022956041677298</v>
       </c>
     </row>
   </sheetData>
